--- a/data/weapons.xlsx
+++ b/data/weapons.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,16 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>muzzle_x</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -480,6 +490,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>pistol</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>기본 원거리</t>
         </is>
       </c>
@@ -509,7 +527,7 @@
       <c r="F3" t="b">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>기본 근접</t>
         </is>
@@ -542,6 +560,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>riffle</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>제작: 높은 데미지</t>
         </is>
       </c>
@@ -571,7 +597,10 @@
       <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>제작: 근거리 강력</t>
         </is>
@@ -602,7 +631,7 @@
       <c r="F6" t="b">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>제작: 강한 근접</t>
         </is>
